--- a/03_Outputs/Bioenergetica_Norte/05_Economia/economia.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/05_Economia/economia.xlsx
@@ -22,6 +22,21 @@
     <sheet name="energia_centrales" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="energia_participacion" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="titulos_mineros" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="_fig_01" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_fig_02" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_fig_03" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_fig_04" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="_fig_05" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="_fig_06" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="_fig_07" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="_fig_08" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="_fig_09" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="_fig_10" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="_fig_11" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="_fig_12" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="_fig_13" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="_fig_14" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="_fig_15" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
 </workbook>
 </file>
@@ -6085,10 +6100,10 @@
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
     <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
     <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="61.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="65.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="67.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="66.711"/>
     <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
     <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
     <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
@@ -6125,22 +6140,22 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Valor agregado total (miles de millones $)</t>
+          <t>Valor agregado total (miles de millones $ constantes de 2015)</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>VA actividades primarias (miles de millones $)</t>
+          <t>VA actividades primarias (miles de millones $ constantes de 2015)</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>VA actividades secundarias (miles de millones $)</t>
+          <t>VA actividades secundarias (miles de millones $ constantes de 2015)</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>VA actividades terciarias (miles de millones $)</t>
+          <t>VA actividades terciarias (miles de millones $ constantes de 2015)</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -23441,6 +23456,524 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_pob_nbi_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.216353395158996</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.309798468910477</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.279741824325051</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.288797013494751</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.147349785257068</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.240858348226192</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.094264600850104</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.209083204069841</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.260575410880246</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.208621765436514</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.155649803990907</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.18658836347785</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.121907730397495</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_pob_ipm_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.284189911642329</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.191364059468404</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.311922572515303</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.385416857911961</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.0737751666956267</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.238546443807948</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.141484307557884</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.269865710529551</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.232173322912713</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.191216067267174</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.154681647228847</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.202516967432283</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.114799296530936</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_gini_hog_mun</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>tot_gini_lab_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.650053913077675</v>
+      </c>
+      <c r="C2">
+        <v>0.55665815723022</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.471866449712182</v>
+      </c>
+      <c r="C3">
+        <v>0.345673201573</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.496607604342832</v>
+      </c>
+      <c r="C4">
+        <v>0.413986576250264</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.510192818421068</v>
+      </c>
+      <c r="C5">
+        <v>0.400251734382689</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.52470140702139</v>
+      </c>
+      <c r="C6">
+        <v>0.439900336075889</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.393782178081221</v>
+      </c>
+      <c r="C7">
+        <v>0.251780176267932</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.3523431320307</v>
+      </c>
+      <c r="C8">
+        <v>0.310111192266797</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.418205573422546</v>
+      </c>
+      <c r="C9">
+        <v>0.280514007132762</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.493736955497255</v>
+      </c>
+      <c r="C10">
+        <v>0.414335415335926</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.535276342244976</v>
+      </c>
+      <c r="C11">
+        <v>0.400826938351011</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.447761132359925</v>
+      </c>
+      <c r="C12">
+        <v>0.340177140910313</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.619385925259623</v>
+      </c>
+      <c r="C13">
+        <v>0.551526358903278</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.513105114430282</v>
+      </c>
+      <c r="C14">
+        <v>0.376042331898138</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:E13"/>
@@ -23705,6 +24238,2005 @@
       </c>
       <c r="E13" s="11">
         <v>0.000191873107917964</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_to_mun</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>tot_emp_informal_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.473018786044298</v>
+      </c>
+      <c r="C2">
+        <v>0.741878238763376</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.520424037157257</v>
+      </c>
+      <c r="C3">
+        <v>0.636818277934877</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.471720091008674</v>
+      </c>
+      <c r="C4">
+        <v>0.765701638532202</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.495592923411277</v>
+      </c>
+      <c r="C5">
+        <v>0.737671178921712</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.418773342670401</v>
+      </c>
+      <c r="C6">
+        <v>0.641391285686532</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.430032844023073</v>
+      </c>
+      <c r="C7">
+        <v>0.560105208868112</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.452846912880949</v>
+      </c>
+      <c r="C8">
+        <v>0.666701948522445</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.491095877124122</v>
+      </c>
+      <c r="C9">
+        <v>0.871879986479892</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.479663852045708</v>
+      </c>
+      <c r="C10">
+        <v>0.710617342571698</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.474107048575371</v>
+      </c>
+      <c r="C11">
+        <v>0.771688761811478</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.526542527333019</v>
+      </c>
+      <c r="C12">
+        <v>0.663925066206372</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.45049154101122</v>
+      </c>
+      <c r="C13">
+        <v>0.801565510549701</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.492797259670368</v>
+      </c>
+      <c r="C14">
+        <v>0.659654721125991</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_td_mun</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>tot_td_15_28_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.0242608180134457</v>
+      </c>
+      <c r="C2">
+        <v>0.0190330646302095</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.0921754236691679</v>
+      </c>
+      <c r="C3">
+        <v>0.106100785882731</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0347024579397613</v>
+      </c>
+      <c r="C4">
+        <v>0.072066700863613</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.00616968007731162</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.0791782890376496</v>
+      </c>
+      <c r="C6">
+        <v>0.100763358778626</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.115729554550753</v>
+      </c>
+      <c r="C7">
+        <v>0.112965351238233</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.099503152359867</v>
+      </c>
+      <c r="C8">
+        <v>0.128414194299785</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.0111798553520305</v>
+      </c>
+      <c r="C9">
+        <v>0.0225785253576186</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.0552671762005844</v>
+      </c>
+      <c r="C10">
+        <v>0.150561886477444</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.0568286824888774</v>
+      </c>
+      <c r="C11">
+        <v>0.0847801761021575</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.0492117025646477</v>
+      </c>
+      <c r="C12">
+        <v>0.0336082411667135</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.034906263762852</v>
+      </c>
+      <c r="C13">
+        <v>0.0880527082540391</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.0843617917924197</v>
+      </c>
+      <c r="C14">
+        <v>0.105837837739972</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_nini_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.286276944098332</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.252218991372124</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.210141604010025</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.252918798373344</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.255376344086022</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.273015653492327</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.326084910716285</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.244885899435532</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.31644871194014</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.345245901639344</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.218076045909071</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.250838303932766</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.307449020183317</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>53.4105210168638</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>55.8282208588957</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>57.837738619677</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>59.5944849959449</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>46.6804979253112</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>50.6334550139575</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>53.5211267605634</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>42.1850547730829</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>58.5702513391018</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>51.111963190184</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>58.0423754103253</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>57.8426152699393</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>50.2147362770098</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>dens_emp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>13.244481086731</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>26.4761619567871</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>11.5661516189575</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>8.06534957885742</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>25.3953037261963</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>10.3956108093262</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>23.6893196105957</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>9.04519081115723</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>17.6362209320068</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>23.5324535369873</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>29.8564586639404</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>10.6193475723267</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>26.4840602874756</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>va_total</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>poblacion</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>va_pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2024</v>
+      </c>
+      <c r="C2">
+        <v>115.904428177988</v>
+      </c>
+      <c r="D2">
+        <v>12121</v>
+      </c>
+      <c r="E2">
+        <v>9562282.66463061</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2024</v>
+      </c>
+      <c r="C3">
+        <v>280.20649862185</v>
+      </c>
+      <c r="D3">
+        <v>19675</v>
+      </c>
+      <c r="E3">
+        <v>14241753.4242363</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2024</v>
+      </c>
+      <c r="C4">
+        <v>93.4441764265579</v>
+      </c>
+      <c r="D4">
+        <v>8523</v>
+      </c>
+      <c r="E4">
+        <v>10963765.8602086</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2024</v>
+      </c>
+      <c r="C5">
+        <v>76.9696320120832</v>
+      </c>
+      <c r="D5">
+        <v>9755</v>
+      </c>
+      <c r="E5">
+        <v>7890274.93716896</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2024</v>
+      </c>
+      <c r="C6">
+        <v>58.2346104602222</v>
+      </c>
+      <c r="D6">
+        <v>4219</v>
+      </c>
+      <c r="E6">
+        <v>13802941.5644044</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>62.8818998199969</v>
+      </c>
+      <c r="D7">
+        <v>6966</v>
+      </c>
+      <c r="E7">
+        <v>9026973.84725766</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2024</v>
+      </c>
+      <c r="C8">
+        <v>348.582334379008</v>
+      </c>
+      <c r="D8">
+        <v>10397</v>
+      </c>
+      <c r="E8">
+        <v>33527203.4605182</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2024</v>
+      </c>
+      <c r="C9">
+        <v>246.438334169422</v>
+      </c>
+      <c r="D9">
+        <v>28890</v>
+      </c>
+      <c r="E9">
+        <v>8530229.635494</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2024</v>
+      </c>
+      <c r="C10">
+        <v>72.2102743472631</v>
+      </c>
+      <c r="D10">
+        <v>7649</v>
+      </c>
+      <c r="E10">
+        <v>9440485.59906695</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2024</v>
+      </c>
+      <c r="C11">
+        <v>37.1643265867581</v>
+      </c>
+      <c r="D11">
+        <v>3920</v>
+      </c>
+      <c r="E11">
+        <v>9480695.55784646</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2024</v>
+      </c>
+      <c r="C12">
+        <v>78.612264158468</v>
+      </c>
+      <c r="D12">
+        <v>5266</v>
+      </c>
+      <c r="E12">
+        <v>14928268.9248895</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2024</v>
+      </c>
+      <c r="C13">
+        <v>134.594216215321</v>
+      </c>
+      <c r="D13">
+        <v>14722</v>
+      </c>
+      <c r="E13">
+        <v>9142386.64687688</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14">
+        <v>608.453893463717</v>
+      </c>
+      <c r="D14">
+        <v>44457</v>
+      </c>
+      <c r="E14">
+        <v>13686346.2101293</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>va_total</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>prop_va_prov</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2024</v>
+      </c>
+      <c r="C2">
+        <v>115.904428177988</v>
+      </c>
+      <c r="D2">
+        <v>0.0523578583691253</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2024</v>
+      </c>
+      <c r="C3">
+        <v>280.20649862185</v>
+      </c>
+      <c r="D3">
+        <v>0.126578530256169</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2024</v>
+      </c>
+      <c r="C4">
+        <v>93.4441764265579</v>
+      </c>
+      <c r="D4">
+        <v>0.042211820822308</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2024</v>
+      </c>
+      <c r="C5">
+        <v>76.9696320120832</v>
+      </c>
+      <c r="D5">
+        <v>0.0347697249791334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2024</v>
+      </c>
+      <c r="C6">
+        <v>58.2346104602222</v>
+      </c>
+      <c r="D6">
+        <v>0.0263064969526036</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>62.8818998199969</v>
+      </c>
+      <c r="D7">
+        <v>0.0284058310498805</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2024</v>
+      </c>
+      <c r="C8">
+        <v>348.582334379008</v>
+      </c>
+      <c r="D8">
+        <v>0.157466153625884</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2024</v>
+      </c>
+      <c r="C9">
+        <v>246.438334169422</v>
+      </c>
+      <c r="D9">
+        <v>0.111324335057772</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2024</v>
+      </c>
+      <c r="C10">
+        <v>72.2102743472631</v>
+      </c>
+      <c r="D10">
+        <v>0.0326197659270082</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2024</v>
+      </c>
+      <c r="C11">
+        <v>37.1643265867581</v>
+      </c>
+      <c r="D11">
+        <v>0.016788353804958</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2024</v>
+      </c>
+      <c r="C12">
+        <v>78.612264158468</v>
+      </c>
+      <c r="D12">
+        <v>0.0355117561734974</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2024</v>
+      </c>
+      <c r="C13">
+        <v>134.594216215321</v>
+      </c>
+      <c r="D13">
+        <v>0.0608006529231434</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14">
+        <v>608.453893463717</v>
+      </c>
+      <c r="D14">
+        <v>0.274858720058518</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Primarias</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Secundarias</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Terciarias</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>No distribuido</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.167397633847718</v>
+      </c>
+      <c r="C2">
+        <v>0.0520200499069344</v>
+      </c>
+      <c r="D2">
+        <v>0.731042607623753</v>
+      </c>
+      <c r="E2">
+        <v>0.0495397086215946</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.322088597797208</v>
+      </c>
+      <c r="C3">
+        <v>0.0310494035610422</v>
+      </c>
+      <c r="D3">
+        <v>0.380414283491504</v>
+      </c>
+      <c r="E3">
+        <v>0.266447715150245</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.204633470429329</v>
+      </c>
+      <c r="C4">
+        <v>0.0437655479086332</v>
+      </c>
+      <c r="D4">
+        <v>0.493088561508998</v>
+      </c>
+      <c r="E4">
+        <v>0.25851242015304</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.119700823687638</v>
+      </c>
+      <c r="C5">
+        <v>0.0533847324779081</v>
+      </c>
+      <c r="D5">
+        <v>0.811236367559816</v>
+      </c>
+      <c r="E5">
+        <v>0.0156780762746385</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.217160796669884</v>
+      </c>
+      <c r="C6">
+        <v>0.0499281507418424</v>
+      </c>
+      <c r="D6">
+        <v>0.501647052735216</v>
+      </c>
+      <c r="E6">
+        <v>0.231263999853057</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.110050134026312</v>
+      </c>
+      <c r="C7">
+        <v>0.0521954771174352</v>
+      </c>
+      <c r="D7">
+        <v>0.641945840098699</v>
+      </c>
+      <c r="E7">
+        <v>0.195808548757554</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.0800095652213455</v>
+      </c>
+      <c r="C8">
+        <v>0.0457915594537504</v>
+      </c>
+      <c r="D8">
+        <v>0.859066671986467</v>
+      </c>
+      <c r="E8">
+        <v>0.0151322033384376</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.143049101009309</v>
+      </c>
+      <c r="C9">
+        <v>0.0536321683117615</v>
+      </c>
+      <c r="D9">
+        <v>0.75278014086484</v>
+      </c>
+      <c r="E9">
+        <v>0.05053858981409</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.1625317676043</v>
+      </c>
+      <c r="C10">
+        <v>0.0519002602962019</v>
+      </c>
+      <c r="D10">
+        <v>0.650902178999945</v>
+      </c>
+      <c r="E10">
+        <v>0.134665793099553</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.101355743507822</v>
+      </c>
+      <c r="C11">
+        <v>0.0535237388098215</v>
+      </c>
+      <c r="D11">
+        <v>0.817937530205637</v>
+      </c>
+      <c r="E11">
+        <v>0.0271829874767191</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.129235853665231</v>
+      </c>
+      <c r="C12">
+        <v>0.0505822012503921</v>
+      </c>
+      <c r="D12">
+        <v>0.768718330406827</v>
+      </c>
+      <c r="E12">
+        <v>0.0514636146775498</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.094099948851965</v>
+      </c>
+      <c r="C13">
+        <v>0.0512783308245559</v>
+      </c>
+      <c r="D13">
+        <v>0.840368507193816</v>
+      </c>
+      <c r="E13">
+        <v>0.0142532131296632</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.0994022203548206</v>
+      </c>
+      <c r="C14">
+        <v>0.261269613667946</v>
+      </c>
+      <c r="D14">
+        <v>0.626420059062822</v>
+      </c>
+      <c r="E14">
+        <v>0.0129081069144112</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>actividad</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Agricultura, ganadería, caza, silvicultura y pesca</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>305.48281638705</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Explotación de minas y canteras</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>13.9208296386977</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Industrias manufactureras</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>166.195963811366</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>67.6866893921377</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Suministro de electricidad, gas y agua</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>245.104209572875</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Comercio, transporte y alojamiento</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>334.825312519506</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Información y comunicaciones</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>59.705238169342</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Actividades financieras y de seguros</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>56.6570551485822</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Actividades inmobiliarias</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>144.345552096688</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actividades profesionales, científicas y técnicas</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>190.513630134679</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Administración pública, educación y salud</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>359.728180878371</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Actividades artísticas y de entretenimiento</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>95.5996903556755</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>mineral</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>n_titulos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mineral de oro</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Carbón metalúrgico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Carbón térmico</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Antracita</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Arenas</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gravas</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mineral de plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Carbón</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Minerales de oro y sus concentrados</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mineral de cobre</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Otros minerales</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -24490,6 +27022,632 @@
       </c>
       <c r="J17" s="23">
         <v>0.153620919392402</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>visitantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2019</v>
+      </c>
+      <c r="C2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2020</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2021</v>
+      </c>
+      <c r="C4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2022</v>
+      </c>
+      <c r="C5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2023</v>
+      </c>
+      <c r="C6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2025</v>
+      </c>
+      <c r="C8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2019</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2020</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2021</v>
+      </c>
+      <c r="C11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2022</v>
+      </c>
+      <c r="C12">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2023</v>
+      </c>
+      <c r="C13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2025</v>
+      </c>
+      <c r="C15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>2019</v>
+      </c>
+      <c r="C16">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>2020</v>
+      </c>
+      <c r="C17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>2021</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>2022</v>
+      </c>
+      <c r="C19">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>2023</v>
+      </c>
+      <c r="C20">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>2024</v>
+      </c>
+      <c r="C21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2025</v>
+      </c>
+      <c r="C22">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>2019</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>2020</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>2021</v>
+      </c>
+      <c r="C25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>2022</v>
+      </c>
+      <c r="C26">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>2023</v>
+      </c>
+      <c r="C27">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>2024</v>
+      </c>
+      <c r="C28">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>2025</v>
+      </c>
+      <c r="C29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>2019</v>
+      </c>
+      <c r="C30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2020</v>
+      </c>
+      <c r="C31">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>2021</v>
+      </c>
+      <c r="C32">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>2022</v>
+      </c>
+      <c r="C33">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>2023</v>
+      </c>
+      <c r="C34">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>2024</v>
+      </c>
+      <c r="C35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>2025</v>
+      </c>
+      <c r="C36">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>total_provincia</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>total_antioquia</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>participacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2019</v>
+      </c>
+      <c r="B2">
+        <v>78</v>
+      </c>
+      <c r="C2">
+        <v>438530</v>
+      </c>
+      <c r="D2">
+        <v>0.000177866964631838</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2020</v>
+      </c>
+      <c r="B3">
+        <v>41</v>
+      </c>
+      <c r="C3">
+        <v>145209</v>
+      </c>
+      <c r="D3">
+        <v>0.000282351644870497</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2021</v>
+      </c>
+      <c r="B4">
+        <v>126</v>
+      </c>
+      <c r="C4">
+        <v>303516</v>
+      </c>
+      <c r="D4">
+        <v>0.000415134622227494</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2022</v>
+      </c>
+      <c r="B5">
+        <v>300</v>
+      </c>
+      <c r="C5">
+        <v>710194</v>
+      </c>
+      <c r="D5">
+        <v>0.0004224197895223</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2023</v>
+      </c>
+      <c r="B6">
+        <v>161</v>
+      </c>
+      <c r="C6">
+        <v>532516</v>
+      </c>
+      <c r="D6">
+        <v>0.000302338333496083</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7">
+        <v>167</v>
+      </c>
+      <c r="C7">
+        <v>905451</v>
+      </c>
+      <c r="D7">
+        <v>0.000184438473202857</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2025</v>
+      </c>
+      <c r="B8">
+        <v>188</v>
+      </c>
+      <c r="C8">
+        <v>1038940</v>
+      </c>
+      <c r="D8">
+        <v>0.000180953664311702</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/Bioenergetica_Norte/05_Economia/economia.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/05_Economia/economia.xlsx
@@ -22,21 +22,6 @@
     <sheet name="energia_centrales" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="energia_participacion" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="titulos_mineros" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="_fig_01" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="_fig_02" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="_fig_03" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="_fig_04" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="_fig_05" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="_fig_06" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="_fig_07" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="_fig_08" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="_fig_09" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="_fig_10" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="_fig_11" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="_fig_12" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="_fig_13" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="_fig_14" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="_fig_15" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
 </workbook>
 </file>
@@ -23456,524 +23441,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>tot_pob_nbi_mun</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>0.216353395158996</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0.309798468910477</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0.279741824325051</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0.288797013494751</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0.147349785257068</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>0.240858348226192</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.094264600850104</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>0.209083204069841</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>0.260575410880246</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0.208621765436514</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>0.155649803990907</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>0.18658836347785</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>0.121907730397495</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>tot_pob_ipm_mun</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>0.284189911642329</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0.191364059468404</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0.311922572515303</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0.385416857911961</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0.0737751666956267</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>0.238546443807948</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.141484307557884</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>0.269865710529551</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>0.232173322912713</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0.191216067267174</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>0.154681647228847</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>0.202516967432283</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>0.114799296530936</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>tot_gini_hog_mun</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>tot_gini_lab_mun</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>0.650053913077675</v>
-      </c>
-      <c r="C2">
-        <v>0.55665815723022</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0.471866449712182</v>
-      </c>
-      <c r="C3">
-        <v>0.345673201573</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0.496607604342832</v>
-      </c>
-      <c r="C4">
-        <v>0.413986576250264</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0.510192818421068</v>
-      </c>
-      <c r="C5">
-        <v>0.400251734382689</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0.52470140702139</v>
-      </c>
-      <c r="C6">
-        <v>0.439900336075889</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>0.393782178081221</v>
-      </c>
-      <c r="C7">
-        <v>0.251780176267932</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.3523431320307</v>
-      </c>
-      <c r="C8">
-        <v>0.310111192266797</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>0.418205573422546</v>
-      </c>
-      <c r="C9">
-        <v>0.280514007132762</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>0.493736955497255</v>
-      </c>
-      <c r="C10">
-        <v>0.414335415335926</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0.535276342244976</v>
-      </c>
-      <c r="C11">
-        <v>0.400826938351011</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>0.447761132359925</v>
-      </c>
-      <c r="C12">
-        <v>0.340177140910313</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>0.619385925259623</v>
-      </c>
-      <c r="C13">
-        <v>0.551526358903278</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>0.513105114430282</v>
-      </c>
-      <c r="C14">
-        <v>0.376042331898138</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:E13"/>
@@ -24238,2005 +23705,6 @@
       </c>
       <c r="E13" s="11">
         <v>0.000191873107917964</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>tot_to_mun</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>tot_emp_informal_mun</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>0.473018786044298</v>
-      </c>
-      <c r="C2">
-        <v>0.741878238763376</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0.520424037157257</v>
-      </c>
-      <c r="C3">
-        <v>0.636818277934877</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0.471720091008674</v>
-      </c>
-      <c r="C4">
-        <v>0.765701638532202</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0.495592923411277</v>
-      </c>
-      <c r="C5">
-        <v>0.737671178921712</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0.418773342670401</v>
-      </c>
-      <c r="C6">
-        <v>0.641391285686532</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>0.430032844023073</v>
-      </c>
-      <c r="C7">
-        <v>0.560105208868112</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.452846912880949</v>
-      </c>
-      <c r="C8">
-        <v>0.666701948522445</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>0.491095877124122</v>
-      </c>
-      <c r="C9">
-        <v>0.871879986479892</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>0.479663852045708</v>
-      </c>
-      <c r="C10">
-        <v>0.710617342571698</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0.474107048575371</v>
-      </c>
-      <c r="C11">
-        <v>0.771688761811478</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>0.526542527333019</v>
-      </c>
-      <c r="C12">
-        <v>0.663925066206372</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>0.45049154101122</v>
-      </c>
-      <c r="C13">
-        <v>0.801565510549701</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>0.492797259670368</v>
-      </c>
-      <c r="C14">
-        <v>0.659654721125991</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>tot_td_mun</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>tot_td_15_28_mun</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>0.0242608180134457</v>
-      </c>
-      <c r="C2">
-        <v>0.0190330646302095</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0.0921754236691679</v>
-      </c>
-      <c r="C3">
-        <v>0.106100785882731</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0.0347024579397613</v>
-      </c>
-      <c r="C4">
-        <v>0.072066700863613</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0.00616968007731162</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0.0791782890376496</v>
-      </c>
-      <c r="C6">
-        <v>0.100763358778626</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>0.115729554550753</v>
-      </c>
-      <c r="C7">
-        <v>0.112965351238233</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.099503152359867</v>
-      </c>
-      <c r="C8">
-        <v>0.128414194299785</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>0.0111798553520305</v>
-      </c>
-      <c r="C9">
-        <v>0.0225785253576186</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>0.0552671762005844</v>
-      </c>
-      <c r="C10">
-        <v>0.150561886477444</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0.0568286824888774</v>
-      </c>
-      <c r="C11">
-        <v>0.0847801761021575</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>0.0492117025646477</v>
-      </c>
-      <c r="C12">
-        <v>0.0336082411667135</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>0.034906263762852</v>
-      </c>
-      <c r="C13">
-        <v>0.0880527082540391</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>0.0843617917924197</v>
-      </c>
-      <c r="C14">
-        <v>0.105837837739972</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>tot_nini_mun</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>0.286276944098332</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0.252218991372124</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0.210141604010025</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0.252918798373344</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0.255376344086022</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>0.273015653492327</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.326084910716285</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>0.244885899435532</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>0.31644871194014</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0.345245901639344</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>0.218076045909071</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>0.250838303932766</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>0.307449020183317</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>ide</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>53.4105210168638</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>55.8282208588957</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>57.837738619677</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>59.5944849959449</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>46.6804979253112</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>50.6334550139575</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>53.5211267605634</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>42.1850547730829</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>58.5702513391018</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>51.111963190184</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>58.0423754103253</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>57.8426152699393</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>50.2147362770098</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>dens_emp</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>13.244481086731</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>26.4761619567871</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>11.5661516189575</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>8.06534957885742</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>25.3953037261963</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>10.3956108093262</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>23.6893196105957</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>9.04519081115723</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>17.6362209320068</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>23.5324535369873</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>29.8564586639404</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>10.6193475723267</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>26.4840602874756</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>anio</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>va_total</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>poblacion</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>va_pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>2024</v>
-      </c>
-      <c r="C2">
-        <v>115.904428177988</v>
-      </c>
-      <c r="D2">
-        <v>12121</v>
-      </c>
-      <c r="E2">
-        <v>9562282.66463061</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>2024</v>
-      </c>
-      <c r="C3">
-        <v>280.20649862185</v>
-      </c>
-      <c r="D3">
-        <v>19675</v>
-      </c>
-      <c r="E3">
-        <v>14241753.4242363</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>2024</v>
-      </c>
-      <c r="C4">
-        <v>93.4441764265579</v>
-      </c>
-      <c r="D4">
-        <v>8523</v>
-      </c>
-      <c r="E4">
-        <v>10963765.8602086</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>2024</v>
-      </c>
-      <c r="C5">
-        <v>76.9696320120832</v>
-      </c>
-      <c r="D5">
-        <v>9755</v>
-      </c>
-      <c r="E5">
-        <v>7890274.93716896</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>2024</v>
-      </c>
-      <c r="C6">
-        <v>58.2346104602222</v>
-      </c>
-      <c r="D6">
-        <v>4219</v>
-      </c>
-      <c r="E6">
-        <v>13802941.5644044</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2024</v>
-      </c>
-      <c r="C7">
-        <v>62.8818998199969</v>
-      </c>
-      <c r="D7">
-        <v>6966</v>
-      </c>
-      <c r="E7">
-        <v>9026973.84725766</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>2024</v>
-      </c>
-      <c r="C8">
-        <v>348.582334379008</v>
-      </c>
-      <c r="D8">
-        <v>10397</v>
-      </c>
-      <c r="E8">
-        <v>33527203.4605182</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2024</v>
-      </c>
-      <c r="C9">
-        <v>246.438334169422</v>
-      </c>
-      <c r="D9">
-        <v>28890</v>
-      </c>
-      <c r="E9">
-        <v>8530229.635494</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>2024</v>
-      </c>
-      <c r="C10">
-        <v>72.2102743472631</v>
-      </c>
-      <c r="D10">
-        <v>7649</v>
-      </c>
-      <c r="E10">
-        <v>9440485.59906695</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>2024</v>
-      </c>
-      <c r="C11">
-        <v>37.1643265867581</v>
-      </c>
-      <c r="D11">
-        <v>3920</v>
-      </c>
-      <c r="E11">
-        <v>9480695.55784646</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>2024</v>
-      </c>
-      <c r="C12">
-        <v>78.612264158468</v>
-      </c>
-      <c r="D12">
-        <v>5266</v>
-      </c>
-      <c r="E12">
-        <v>14928268.9248895</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>2024</v>
-      </c>
-      <c r="C13">
-        <v>134.594216215321</v>
-      </c>
-      <c r="D13">
-        <v>14722</v>
-      </c>
-      <c r="E13">
-        <v>9142386.64687688</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>2024</v>
-      </c>
-      <c r="C14">
-        <v>608.453893463717</v>
-      </c>
-      <c r="D14">
-        <v>44457</v>
-      </c>
-      <c r="E14">
-        <v>13686346.2101293</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>anio</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>va_total</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>prop_va_prov</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>2024</v>
-      </c>
-      <c r="C2">
-        <v>115.904428177988</v>
-      </c>
-      <c r="D2">
-        <v>0.0523578583691253</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>2024</v>
-      </c>
-      <c r="C3">
-        <v>280.20649862185</v>
-      </c>
-      <c r="D3">
-        <v>0.126578530256169</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>2024</v>
-      </c>
-      <c r="C4">
-        <v>93.4441764265579</v>
-      </c>
-      <c r="D4">
-        <v>0.042211820822308</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>2024</v>
-      </c>
-      <c r="C5">
-        <v>76.9696320120832</v>
-      </c>
-      <c r="D5">
-        <v>0.0347697249791334</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>2024</v>
-      </c>
-      <c r="C6">
-        <v>58.2346104602222</v>
-      </c>
-      <c r="D6">
-        <v>0.0263064969526036</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2024</v>
-      </c>
-      <c r="C7">
-        <v>62.8818998199969</v>
-      </c>
-      <c r="D7">
-        <v>0.0284058310498805</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>2024</v>
-      </c>
-      <c r="C8">
-        <v>348.582334379008</v>
-      </c>
-      <c r="D8">
-        <v>0.157466153625884</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2024</v>
-      </c>
-      <c r="C9">
-        <v>246.438334169422</v>
-      </c>
-      <c r="D9">
-        <v>0.111324335057772</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>2024</v>
-      </c>
-      <c r="C10">
-        <v>72.2102743472631</v>
-      </c>
-      <c r="D10">
-        <v>0.0326197659270082</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>2024</v>
-      </c>
-      <c r="C11">
-        <v>37.1643265867581</v>
-      </c>
-      <c r="D11">
-        <v>0.016788353804958</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>2024</v>
-      </c>
-      <c r="C12">
-        <v>78.612264158468</v>
-      </c>
-      <c r="D12">
-        <v>0.0355117561734974</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>2024</v>
-      </c>
-      <c r="C13">
-        <v>134.594216215321</v>
-      </c>
-      <c r="D13">
-        <v>0.0608006529231434</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>2024</v>
-      </c>
-      <c r="C14">
-        <v>608.453893463717</v>
-      </c>
-      <c r="D14">
-        <v>0.274858720058518</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Primarias</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Secundarias</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Terciarias</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>No distribuido</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>0.167397633847718</v>
-      </c>
-      <c r="C2">
-        <v>0.0520200499069344</v>
-      </c>
-      <c r="D2">
-        <v>0.731042607623753</v>
-      </c>
-      <c r="E2">
-        <v>0.0495397086215946</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0.322088597797208</v>
-      </c>
-      <c r="C3">
-        <v>0.0310494035610422</v>
-      </c>
-      <c r="D3">
-        <v>0.380414283491504</v>
-      </c>
-      <c r="E3">
-        <v>0.266447715150245</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0.204633470429329</v>
-      </c>
-      <c r="C4">
-        <v>0.0437655479086332</v>
-      </c>
-      <c r="D4">
-        <v>0.493088561508998</v>
-      </c>
-      <c r="E4">
-        <v>0.25851242015304</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0.119700823687638</v>
-      </c>
-      <c r="C5">
-        <v>0.0533847324779081</v>
-      </c>
-      <c r="D5">
-        <v>0.811236367559816</v>
-      </c>
-      <c r="E5">
-        <v>0.0156780762746385</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0.217160796669884</v>
-      </c>
-      <c r="C6">
-        <v>0.0499281507418424</v>
-      </c>
-      <c r="D6">
-        <v>0.501647052735216</v>
-      </c>
-      <c r="E6">
-        <v>0.231263999853057</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>0.110050134026312</v>
-      </c>
-      <c r="C7">
-        <v>0.0521954771174352</v>
-      </c>
-      <c r="D7">
-        <v>0.641945840098699</v>
-      </c>
-      <c r="E7">
-        <v>0.195808548757554</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.0800095652213455</v>
-      </c>
-      <c r="C8">
-        <v>0.0457915594537504</v>
-      </c>
-      <c r="D8">
-        <v>0.859066671986467</v>
-      </c>
-      <c r="E8">
-        <v>0.0151322033384376</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>0.143049101009309</v>
-      </c>
-      <c r="C9">
-        <v>0.0536321683117615</v>
-      </c>
-      <c r="D9">
-        <v>0.75278014086484</v>
-      </c>
-      <c r="E9">
-        <v>0.05053858981409</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>0.1625317676043</v>
-      </c>
-      <c r="C10">
-        <v>0.0519002602962019</v>
-      </c>
-      <c r="D10">
-        <v>0.650902178999945</v>
-      </c>
-      <c r="E10">
-        <v>0.134665793099553</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0.101355743507822</v>
-      </c>
-      <c r="C11">
-        <v>0.0535237388098215</v>
-      </c>
-      <c r="D11">
-        <v>0.817937530205637</v>
-      </c>
-      <c r="E11">
-        <v>0.0271829874767191</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>0.129235853665231</v>
-      </c>
-      <c r="C12">
-        <v>0.0505822012503921</v>
-      </c>
-      <c r="D12">
-        <v>0.768718330406827</v>
-      </c>
-      <c r="E12">
-        <v>0.0514636146775498</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>0.094099948851965</v>
-      </c>
-      <c r="C13">
-        <v>0.0512783308245559</v>
-      </c>
-      <c r="D13">
-        <v>0.840368507193816</v>
-      </c>
-      <c r="E13">
-        <v>0.0142532131296632</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>0.0994022203548206</v>
-      </c>
-      <c r="C14">
-        <v>0.261269613667946</v>
-      </c>
-      <c r="D14">
-        <v>0.626420059062822</v>
-      </c>
-      <c r="E14">
-        <v>0.0129081069144112</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>actividad</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Agricultura, ganadería, caza, silvicultura y pesca</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>305.48281638705</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Explotación de minas y canteras</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>13.9208296386977</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Industrias manufactureras</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>166.195963811366</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Construcción</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>67.6866893921377</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Suministro de electricidad, gas y agua</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>245.104209572875</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Comercio, transporte y alojamiento</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>334.825312519506</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Información y comunicaciones</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>59.705238169342</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Actividades financieras y de seguros</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>56.6570551485822</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Actividades inmobiliarias</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>144.345552096688</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Actividades profesionales, científicas y técnicas</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>190.513630134679</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Administración pública, educación y salud</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>359.728180878371</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Actividades artísticas y de entretenimiento</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>95.5996903556755</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>mineral</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>n_titulos</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Mineral de oro</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Carbón metalúrgico</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Carbón térmico</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Antracita</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Arenas</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Gravas</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mineral de plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Carbón</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Minerales de oro y sus concentrados</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Mineral de cobre</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Otros minerales</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -27022,632 +24490,6 @@
       </c>
       <c r="J17" s="23">
         <v>0.153620919392402</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>serie</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>anio</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>visitantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>2019</v>
-      </c>
-      <c r="C2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>2020</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>2021</v>
-      </c>
-      <c r="C4">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>2022</v>
-      </c>
-      <c r="C5">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>2023</v>
-      </c>
-      <c r="C6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2024</v>
-      </c>
-      <c r="C7">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>2025</v>
-      </c>
-      <c r="C8">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2019</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>2020</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>2021</v>
-      </c>
-      <c r="C11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>2022</v>
-      </c>
-      <c r="C12">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>2023</v>
-      </c>
-      <c r="C13">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>2024</v>
-      </c>
-      <c r="C14">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>2025</v>
-      </c>
-      <c r="C15">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>2019</v>
-      </c>
-      <c r="C16">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>2020</v>
-      </c>
-      <c r="C17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>2021</v>
-      </c>
-      <c r="C18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>2022</v>
-      </c>
-      <c r="C19">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>2023</v>
-      </c>
-      <c r="C20">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>2024</v>
-      </c>
-      <c r="C21">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>2025</v>
-      </c>
-      <c r="C22">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>2019</v>
-      </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>2020</v>
-      </c>
-      <c r="C24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>2021</v>
-      </c>
-      <c r="C25">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>2022</v>
-      </c>
-      <c r="C26">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>2023</v>
-      </c>
-      <c r="C27">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>2024</v>
-      </c>
-      <c r="C28">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>2025</v>
-      </c>
-      <c r="C29">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Otros municipios</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>2019</v>
-      </c>
-      <c r="C30">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Otros municipios</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>2020</v>
-      </c>
-      <c r="C31">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Otros municipios</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>2021</v>
-      </c>
-      <c r="C32">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Otros municipios</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>2022</v>
-      </c>
-      <c r="C33">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Otros municipios</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>2023</v>
-      </c>
-      <c r="C34">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Otros municipios</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>2024</v>
-      </c>
-      <c r="C35">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Otros municipios</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>2025</v>
-      </c>
-      <c r="C36">
-        <v>57</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>anio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>total_provincia</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>total_antioquia</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>participacion</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>2019</v>
-      </c>
-      <c r="B2">
-        <v>78</v>
-      </c>
-      <c r="C2">
-        <v>438530</v>
-      </c>
-      <c r="D2">
-        <v>0.000177866964631838</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2020</v>
-      </c>
-      <c r="B3">
-        <v>41</v>
-      </c>
-      <c r="C3">
-        <v>145209</v>
-      </c>
-      <c r="D3">
-        <v>0.000282351644870497</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>2021</v>
-      </c>
-      <c r="B4">
-        <v>126</v>
-      </c>
-      <c r="C4">
-        <v>303516</v>
-      </c>
-      <c r="D4">
-        <v>0.000415134622227494</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>2022</v>
-      </c>
-      <c r="B5">
-        <v>300</v>
-      </c>
-      <c r="C5">
-        <v>710194</v>
-      </c>
-      <c r="D5">
-        <v>0.0004224197895223</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>2023</v>
-      </c>
-      <c r="B6">
-        <v>161</v>
-      </c>
-      <c r="C6">
-        <v>532516</v>
-      </c>
-      <c r="D6">
-        <v>0.000302338333496083</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>2024</v>
-      </c>
-      <c r="B7">
-        <v>167</v>
-      </c>
-      <c r="C7">
-        <v>905451</v>
-      </c>
-      <c r="D7">
-        <v>0.000184438473202857</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>2025</v>
-      </c>
-      <c r="B8">
-        <v>188</v>
-      </c>
-      <c r="C8">
-        <v>1038940</v>
-      </c>
-      <c r="D8">
-        <v>0.000180953664311702</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/Bioenergetica_Norte/05_Economia/economia.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/05_Economia/economia.xlsx
@@ -22,6 +22,21 @@
     <sheet name="energia_centrales" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="energia_participacion" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="titulos_mineros" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="_fig_01" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_fig_02" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_fig_03" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_fig_04" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="_fig_05" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="_fig_06" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="_fig_07" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="_fig_08" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="_fig_09" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="_fig_10" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="_fig_11" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="_fig_12" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="_fig_13" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="_fig_14" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="_fig_15" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
 </workbook>
 </file>
@@ -23441,6 +23456,524 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_pob_nbi_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.216353395158996</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.309798468910477</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.279741824325051</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.288797013494751</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.147349785257068</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.240858348226192</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.094264600850104</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.209083204069841</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.260575410880246</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.208621765436514</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.155649803990907</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.18658836347785</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.121907730397495</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_pob_ipm_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.284189911642329</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.191364059468404</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.311922572515303</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.385416857911961</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.0737751666956267</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.238546443807948</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.141484307557884</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.269865710529551</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.232173322912713</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.191216067267174</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.154681647228847</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.202516967432283</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.114799296530936</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_gini_hog_mun</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>tot_gini_lab_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.650053913077675</v>
+      </c>
+      <c r="C2">
+        <v>0.55665815723022</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.471866449712182</v>
+      </c>
+      <c r="C3">
+        <v>0.345673201573</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.496607604342832</v>
+      </c>
+      <c r="C4">
+        <v>0.413986576250264</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.510192818421068</v>
+      </c>
+      <c r="C5">
+        <v>0.400251734382689</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.52470140702139</v>
+      </c>
+      <c r="C6">
+        <v>0.439900336075889</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.393782178081221</v>
+      </c>
+      <c r="C7">
+        <v>0.251780176267932</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.3523431320307</v>
+      </c>
+      <c r="C8">
+        <v>0.310111192266797</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.418205573422546</v>
+      </c>
+      <c r="C9">
+        <v>0.280514007132762</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.493736955497255</v>
+      </c>
+      <c r="C10">
+        <v>0.414335415335926</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.535276342244976</v>
+      </c>
+      <c r="C11">
+        <v>0.400826938351011</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.447761132359925</v>
+      </c>
+      <c r="C12">
+        <v>0.340177140910313</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.619385925259623</v>
+      </c>
+      <c r="C13">
+        <v>0.551526358903278</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.513105114430282</v>
+      </c>
+      <c r="C14">
+        <v>0.376042331898138</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:E13"/>
@@ -23705,6 +24238,2005 @@
       </c>
       <c r="E13" s="11">
         <v>0.000191873107917964</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_to_mun</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>tot_emp_informal_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.473018786044298</v>
+      </c>
+      <c r="C2">
+        <v>0.741878238763376</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.520424037157257</v>
+      </c>
+      <c r="C3">
+        <v>0.636818277934877</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.471720091008674</v>
+      </c>
+      <c r="C4">
+        <v>0.765701638532202</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.495592923411277</v>
+      </c>
+      <c r="C5">
+        <v>0.737671178921712</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.418773342670401</v>
+      </c>
+      <c r="C6">
+        <v>0.641391285686532</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.430032844023073</v>
+      </c>
+      <c r="C7">
+        <v>0.560105208868112</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.452846912880949</v>
+      </c>
+      <c r="C8">
+        <v>0.666701948522445</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.491095877124122</v>
+      </c>
+      <c r="C9">
+        <v>0.871879986479892</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.479663852045708</v>
+      </c>
+      <c r="C10">
+        <v>0.710617342571698</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.474107048575371</v>
+      </c>
+      <c r="C11">
+        <v>0.771688761811478</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.526542527333019</v>
+      </c>
+      <c r="C12">
+        <v>0.663925066206372</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.45049154101122</v>
+      </c>
+      <c r="C13">
+        <v>0.801565510549701</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.492797259670368</v>
+      </c>
+      <c r="C14">
+        <v>0.659654721125991</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_td_mun</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>tot_td_15_28_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.0242608180134457</v>
+      </c>
+      <c r="C2">
+        <v>0.0190330646302095</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.0921754236691679</v>
+      </c>
+      <c r="C3">
+        <v>0.106100785882731</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0347024579397613</v>
+      </c>
+      <c r="C4">
+        <v>0.072066700863613</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.00616968007731162</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.0791782890376496</v>
+      </c>
+      <c r="C6">
+        <v>0.100763358778626</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.115729554550753</v>
+      </c>
+      <c r="C7">
+        <v>0.112965351238233</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.099503152359867</v>
+      </c>
+      <c r="C8">
+        <v>0.128414194299785</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.0111798553520305</v>
+      </c>
+      <c r="C9">
+        <v>0.0225785253576186</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.0552671762005844</v>
+      </c>
+      <c r="C10">
+        <v>0.150561886477444</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.0568286824888774</v>
+      </c>
+      <c r="C11">
+        <v>0.0847801761021575</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.0492117025646477</v>
+      </c>
+      <c r="C12">
+        <v>0.0336082411667135</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.034906263762852</v>
+      </c>
+      <c r="C13">
+        <v>0.0880527082540391</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.0843617917924197</v>
+      </c>
+      <c r="C14">
+        <v>0.105837837739972</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_nini_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.286276944098332</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.252218991372124</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.210141604010025</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.252918798373344</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.255376344086022</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.273015653492327</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.326084910716285</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.244885899435532</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.31644871194014</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.345245901639344</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.218076045909071</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.250838303932766</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.307449020183317</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>53.4105210168638</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>55.8282208588957</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>57.837738619677</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>59.5944849959449</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>46.6804979253112</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>50.6334550139575</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>53.5211267605634</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>42.1850547730829</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>58.5702513391018</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>51.111963190184</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>58.0423754103253</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>57.8426152699393</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>50.2147362770098</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>dens_emp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>13.244481086731</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>26.4761619567871</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>11.5661516189575</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>8.06534957885742</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>25.3953037261963</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>10.3956108093262</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>23.6893196105957</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>9.04519081115723</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>17.6362209320068</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>23.5324535369873</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>29.8564586639404</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>10.6193475723267</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>26.4840602874756</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>va_total</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>poblacion</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>va_pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2024</v>
+      </c>
+      <c r="C2">
+        <v>115.904428177988</v>
+      </c>
+      <c r="D2">
+        <v>12121</v>
+      </c>
+      <c r="E2">
+        <v>9562282.66463061</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2024</v>
+      </c>
+      <c r="C3">
+        <v>280.20649862185</v>
+      </c>
+      <c r="D3">
+        <v>19675</v>
+      </c>
+      <c r="E3">
+        <v>14241753.4242363</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2024</v>
+      </c>
+      <c r="C4">
+        <v>93.4441764265579</v>
+      </c>
+      <c r="D4">
+        <v>8523</v>
+      </c>
+      <c r="E4">
+        <v>10963765.8602086</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2024</v>
+      </c>
+      <c r="C5">
+        <v>76.9696320120832</v>
+      </c>
+      <c r="D5">
+        <v>9755</v>
+      </c>
+      <c r="E5">
+        <v>7890274.93716896</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2024</v>
+      </c>
+      <c r="C6">
+        <v>58.2346104602222</v>
+      </c>
+      <c r="D6">
+        <v>4219</v>
+      </c>
+      <c r="E6">
+        <v>13802941.5644044</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>62.8818998199969</v>
+      </c>
+      <c r="D7">
+        <v>6966</v>
+      </c>
+      <c r="E7">
+        <v>9026973.84725766</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2024</v>
+      </c>
+      <c r="C8">
+        <v>348.582334379008</v>
+      </c>
+      <c r="D8">
+        <v>10397</v>
+      </c>
+      <c r="E8">
+        <v>33527203.4605182</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2024</v>
+      </c>
+      <c r="C9">
+        <v>246.438334169422</v>
+      </c>
+      <c r="D9">
+        <v>28890</v>
+      </c>
+      <c r="E9">
+        <v>8530229.635494</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2024</v>
+      </c>
+      <c r="C10">
+        <v>72.2102743472631</v>
+      </c>
+      <c r="D10">
+        <v>7649</v>
+      </c>
+      <c r="E10">
+        <v>9440485.59906695</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2024</v>
+      </c>
+      <c r="C11">
+        <v>37.1643265867581</v>
+      </c>
+      <c r="D11">
+        <v>3920</v>
+      </c>
+      <c r="E11">
+        <v>9480695.55784646</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2024</v>
+      </c>
+      <c r="C12">
+        <v>78.612264158468</v>
+      </c>
+      <c r="D12">
+        <v>5266</v>
+      </c>
+      <c r="E12">
+        <v>14928268.9248895</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2024</v>
+      </c>
+      <c r="C13">
+        <v>134.594216215321</v>
+      </c>
+      <c r="D13">
+        <v>14722</v>
+      </c>
+      <c r="E13">
+        <v>9142386.64687688</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14">
+        <v>608.453893463717</v>
+      </c>
+      <c r="D14">
+        <v>44457</v>
+      </c>
+      <c r="E14">
+        <v>13686346.2101293</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>va_total</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>prop_va_prov</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2024</v>
+      </c>
+      <c r="C2">
+        <v>115.904428177988</v>
+      </c>
+      <c r="D2">
+        <v>0.0523578583691253</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2024</v>
+      </c>
+      <c r="C3">
+        <v>280.20649862185</v>
+      </c>
+      <c r="D3">
+        <v>0.126578530256169</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2024</v>
+      </c>
+      <c r="C4">
+        <v>93.4441764265579</v>
+      </c>
+      <c r="D4">
+        <v>0.042211820822308</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2024</v>
+      </c>
+      <c r="C5">
+        <v>76.9696320120832</v>
+      </c>
+      <c r="D5">
+        <v>0.0347697249791334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2024</v>
+      </c>
+      <c r="C6">
+        <v>58.2346104602222</v>
+      </c>
+      <c r="D6">
+        <v>0.0263064969526036</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>62.8818998199969</v>
+      </c>
+      <c r="D7">
+        <v>0.0284058310498805</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2024</v>
+      </c>
+      <c r="C8">
+        <v>348.582334379008</v>
+      </c>
+      <c r="D8">
+        <v>0.157466153625884</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2024</v>
+      </c>
+      <c r="C9">
+        <v>246.438334169422</v>
+      </c>
+      <c r="D9">
+        <v>0.111324335057772</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2024</v>
+      </c>
+      <c r="C10">
+        <v>72.2102743472631</v>
+      </c>
+      <c r="D10">
+        <v>0.0326197659270082</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2024</v>
+      </c>
+      <c r="C11">
+        <v>37.1643265867581</v>
+      </c>
+      <c r="D11">
+        <v>0.016788353804958</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2024</v>
+      </c>
+      <c r="C12">
+        <v>78.612264158468</v>
+      </c>
+      <c r="D12">
+        <v>0.0355117561734974</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2024</v>
+      </c>
+      <c r="C13">
+        <v>134.594216215321</v>
+      </c>
+      <c r="D13">
+        <v>0.0608006529231434</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14">
+        <v>608.453893463717</v>
+      </c>
+      <c r="D14">
+        <v>0.274858720058518</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Primarias</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Secundarias</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Terciarias</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>No distribuido</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.167397633847718</v>
+      </c>
+      <c r="C2">
+        <v>0.0520200499069344</v>
+      </c>
+      <c r="D2">
+        <v>0.731042607623753</v>
+      </c>
+      <c r="E2">
+        <v>0.0495397086215946</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.322088597797208</v>
+      </c>
+      <c r="C3">
+        <v>0.0310494035610422</v>
+      </c>
+      <c r="D3">
+        <v>0.380414283491504</v>
+      </c>
+      <c r="E3">
+        <v>0.266447715150245</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.204633470429329</v>
+      </c>
+      <c r="C4">
+        <v>0.0437655479086332</v>
+      </c>
+      <c r="D4">
+        <v>0.493088561508998</v>
+      </c>
+      <c r="E4">
+        <v>0.25851242015304</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.119700823687638</v>
+      </c>
+      <c r="C5">
+        <v>0.0533847324779081</v>
+      </c>
+      <c r="D5">
+        <v>0.811236367559816</v>
+      </c>
+      <c r="E5">
+        <v>0.0156780762746385</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.217160796669884</v>
+      </c>
+      <c r="C6">
+        <v>0.0499281507418424</v>
+      </c>
+      <c r="D6">
+        <v>0.501647052735216</v>
+      </c>
+      <c r="E6">
+        <v>0.231263999853057</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.110050134026312</v>
+      </c>
+      <c r="C7">
+        <v>0.0521954771174352</v>
+      </c>
+      <c r="D7">
+        <v>0.641945840098699</v>
+      </c>
+      <c r="E7">
+        <v>0.195808548757554</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.0800095652213455</v>
+      </c>
+      <c r="C8">
+        <v>0.0457915594537504</v>
+      </c>
+      <c r="D8">
+        <v>0.859066671986467</v>
+      </c>
+      <c r="E8">
+        <v>0.0151322033384376</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.143049101009309</v>
+      </c>
+      <c r="C9">
+        <v>0.0536321683117615</v>
+      </c>
+      <c r="D9">
+        <v>0.75278014086484</v>
+      </c>
+      <c r="E9">
+        <v>0.05053858981409</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.1625317676043</v>
+      </c>
+      <c r="C10">
+        <v>0.0519002602962019</v>
+      </c>
+      <c r="D10">
+        <v>0.650902178999945</v>
+      </c>
+      <c r="E10">
+        <v>0.134665793099553</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.101355743507822</v>
+      </c>
+      <c r="C11">
+        <v>0.0535237388098215</v>
+      </c>
+      <c r="D11">
+        <v>0.817937530205637</v>
+      </c>
+      <c r="E11">
+        <v>0.0271829874767191</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.129235853665231</v>
+      </c>
+      <c r="C12">
+        <v>0.0505822012503921</v>
+      </c>
+      <c r="D12">
+        <v>0.768718330406827</v>
+      </c>
+      <c r="E12">
+        <v>0.0514636146775498</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.094099948851965</v>
+      </c>
+      <c r="C13">
+        <v>0.0512783308245559</v>
+      </c>
+      <c r="D13">
+        <v>0.840368507193816</v>
+      </c>
+      <c r="E13">
+        <v>0.0142532131296632</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.0994022203548206</v>
+      </c>
+      <c r="C14">
+        <v>0.261269613667946</v>
+      </c>
+      <c r="D14">
+        <v>0.626420059062822</v>
+      </c>
+      <c r="E14">
+        <v>0.0129081069144112</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>actividad</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Agricultura, ganadería, caza, silvicultura y pesca</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>305.48281638705</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Explotación de minas y canteras</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>13.9208296386977</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Industrias manufactureras</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>166.195963811366</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>67.6866893921377</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Suministro de electricidad, gas y agua</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>245.104209572875</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Comercio, transporte y alojamiento</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>334.825312519506</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Información y comunicaciones</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>59.705238169342</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Actividades financieras y de seguros</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>56.6570551485822</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Actividades inmobiliarias</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>144.345552096688</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actividades profesionales, científicas y técnicas</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>190.513630134679</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Administración pública, educación y salud</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>359.728180878371</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Actividades artísticas y de entretenimiento</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>95.5996903556755</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>mineral</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>n_titulos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mineral de oro</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Carbón metalúrgico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Carbón térmico</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Antracita</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Arenas</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gravas</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mineral de plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Carbón</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Minerales de oro y sus concentrados</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mineral de cobre</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Otros minerales</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -24490,6 +27022,632 @@
       </c>
       <c r="J17" s="23">
         <v>0.153620919392402</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>visitantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2019</v>
+      </c>
+      <c r="C2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2020</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2021</v>
+      </c>
+      <c r="C4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2022</v>
+      </c>
+      <c r="C5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2023</v>
+      </c>
+      <c r="C6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2025</v>
+      </c>
+      <c r="C8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2019</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2020</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2021</v>
+      </c>
+      <c r="C11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2022</v>
+      </c>
+      <c r="C12">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2023</v>
+      </c>
+      <c r="C13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2025</v>
+      </c>
+      <c r="C15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>2019</v>
+      </c>
+      <c r="C16">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>2020</v>
+      </c>
+      <c r="C17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>2021</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>2022</v>
+      </c>
+      <c r="C19">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>2023</v>
+      </c>
+      <c r="C20">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>2024</v>
+      </c>
+      <c r="C21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2025</v>
+      </c>
+      <c r="C22">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>2019</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>2020</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>2021</v>
+      </c>
+      <c r="C25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>2022</v>
+      </c>
+      <c r="C26">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>2023</v>
+      </c>
+      <c r="C27">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>2024</v>
+      </c>
+      <c r="C28">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>2025</v>
+      </c>
+      <c r="C29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>2019</v>
+      </c>
+      <c r="C30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2020</v>
+      </c>
+      <c r="C31">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>2021</v>
+      </c>
+      <c r="C32">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>2022</v>
+      </c>
+      <c r="C33">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>2023</v>
+      </c>
+      <c r="C34">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>2024</v>
+      </c>
+      <c r="C35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>2025</v>
+      </c>
+      <c r="C36">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>total_provincia</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>total_antioquia</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>participacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2019</v>
+      </c>
+      <c r="B2">
+        <v>78</v>
+      </c>
+      <c r="C2">
+        <v>438530</v>
+      </c>
+      <c r="D2">
+        <v>0.000177866964631838</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2020</v>
+      </c>
+      <c r="B3">
+        <v>41</v>
+      </c>
+      <c r="C3">
+        <v>145209</v>
+      </c>
+      <c r="D3">
+        <v>0.000282351644870497</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2021</v>
+      </c>
+      <c r="B4">
+        <v>126</v>
+      </c>
+      <c r="C4">
+        <v>303516</v>
+      </c>
+      <c r="D4">
+        <v>0.000415134622227494</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2022</v>
+      </c>
+      <c r="B5">
+        <v>300</v>
+      </c>
+      <c r="C5">
+        <v>710194</v>
+      </c>
+      <c r="D5">
+        <v>0.0004224197895223</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2023</v>
+      </c>
+      <c r="B6">
+        <v>161</v>
+      </c>
+      <c r="C6">
+        <v>532516</v>
+      </c>
+      <c r="D6">
+        <v>0.000302338333496083</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7">
+        <v>167</v>
+      </c>
+      <c r="C7">
+        <v>905451</v>
+      </c>
+      <c r="D7">
+        <v>0.000184438473202857</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2025</v>
+      </c>
+      <c r="B8">
+        <v>188</v>
+      </c>
+      <c r="C8">
+        <v>1038940</v>
+      </c>
+      <c r="D8">
+        <v>0.000180953664311702</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/Bioenergetica_Norte/05_Economia/economia.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/05_Economia/economia.xlsx
@@ -13890,10 +13890,8 @@
       <c r="F4" s="118">
         <v>11.3763842359199</v>
       </c>
-      <c r="G4" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G4" s="120">
+        <v>0.0400751382100002</v>
       </c>
       <c r="H4" s="122">
         <v>0.456315815690001</v>
@@ -14482,10 +14480,8 @@
       <c r="F14" s="118">
         <v>47.0620745815797</v>
       </c>
-      <c r="G14" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G14" s="120">
+        <v>0.0699503590700003</v>
       </c>
       <c r="H14" s="122">
         <v>75.0636137777901</v>
@@ -14546,7 +14542,7 @@
         <v>197.662023725139</v>
       </c>
       <c r="G15" s="121">
-        <v>50.8017092924902</v>
+        <v>50.9117347897702</v>
       </c>
       <c r="H15" s="123">
         <v>123.96070405818</v>
@@ -15312,10 +15308,8 @@
       <c r="F28" s="118">
         <v>41.5215767742668</v>
       </c>
-      <c r="G28" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G28" s="120">
+        <v>0.0923063015017407</v>
       </c>
       <c r="H28" s="122">
         <v>82.8998044532383</v>
@@ -15376,7 +15370,7 @@
         <v>190.234788187666</v>
       </c>
       <c r="G29" s="121">
-        <v>69.0435508009696</v>
+        <v>69.1358571024713</v>
       </c>
       <c r="H29" s="123">
         <v>129.299499418249</v>
@@ -15788,10 +15782,8 @@
       <c r="F36" s="118">
         <v>17.8331978560183</v>
       </c>
-      <c r="G36" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G36" s="120">
+        <v>0.0599597970441284</v>
       </c>
       <c r="H36" s="122">
         <v>13.4836202749466</v>
@@ -16206,7 +16198,7 @@
         <v>192.94868351389</v>
       </c>
       <c r="G43" s="121">
-        <v>17.7995576422841</v>
+        <v>17.8595174393283</v>
       </c>
       <c r="H43" s="123">
         <v>133.990276817431</v>
@@ -16441,10 +16433,8 @@
       <c r="F47" s="118">
         <v>6.16593194612481</v>
       </c>
-      <c r="G47" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G47" s="120">
+        <v>0.0076046013928228</v>
       </c>
       <c r="H47" s="122">
         <v>1.43706844822063</v>
@@ -16620,10 +16610,8 @@
       <c r="F50" s="118">
         <v>19.8312633274314</v>
       </c>
-      <c r="G50" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G50" s="120">
+        <v>0.00776850766108946</v>
       </c>
       <c r="H50" s="122">
         <v>13.4496786171248</v>
@@ -17038,7 +17026,7 @@
         <v>205.386114920528</v>
       </c>
       <c r="G57" s="121">
-        <v>10.217044774852</v>
+        <v>10.2324178839059</v>
       </c>
       <c r="H57" s="123">
         <v>107.598298533601</v>
@@ -18573,10 +18561,8 @@
       <c r="F83" s="118">
         <v>11.0734122840478</v>
       </c>
-      <c r="G83" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G83" s="120">
+        <v>0.0483806553796061</v>
       </c>
       <c r="H83" s="122">
         <v>1.91566182112847</v>
@@ -18634,10 +18620,8 @@
       <c r="F84" s="118">
         <v>32.3239300113556</v>
       </c>
-      <c r="G84" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G84" s="120">
+        <v>0.0398999400114238</v>
       </c>
       <c r="H84" s="122">
         <v>78.6086514909709</v>
@@ -18698,7 +18682,7 @@
         <v>195.238569519258</v>
       </c>
       <c r="G85" s="121">
-        <v>15.5535415578345</v>
+        <v>15.6418221532255</v>
       </c>
       <c r="H85" s="123">
         <v>104.69817601041</v>
@@ -19464,10 +19448,8 @@
       <c r="F98" s="118">
         <v>48.6640510881997</v>
       </c>
-      <c r="G98" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G98" s="120">
+        <v>0.0555533486858533</v>
       </c>
       <c r="H98" s="122">
         <v>140.898918134116</v>
@@ -19528,7 +19510,7 @@
         <v>262.299957464862</v>
       </c>
       <c r="G99" s="121">
-        <v>23.8467871749091</v>
+        <v>23.902340523595</v>
       </c>
       <c r="H99" s="123">
         <v>197.782498702901</v>
@@ -19822,10 +19804,8 @@
       <c r="F104" s="118">
         <v>9.56974786739471</v>
       </c>
-      <c r="G104" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G104" s="120">
+        <v>0.00641584926903257</v>
       </c>
       <c r="H104" s="122">
         <v>0.57642958434259</v>
@@ -20296,10 +20276,8 @@
       <c r="F112" s="118">
         <v>53.708058853098</v>
       </c>
-      <c r="G112" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G112" s="120">
+        <v>0.0559431037720238</v>
       </c>
       <c r="H112" s="122">
         <v>137.201809472311</v>
@@ -20360,7 +20338,7 @@
         <v>237.84354288427</v>
       </c>
       <c r="G113" s="121">
-        <v>58.063477909099</v>
+        <v>58.1258368621401</v>
       </c>
       <c r="H113" s="123">
         <v>166.092769145942</v>
@@ -20654,10 +20632,8 @@
       <c r="F118" s="118">
         <v>11.8855188316341</v>
       </c>
-      <c r="G118" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G118" s="120">
+        <v>0.029908721689811</v>
       </c>
       <c r="H118" s="122">
         <v>0.792986034476234</v>
@@ -21128,10 +21104,8 @@
       <c r="F126" s="118">
         <v>56.9575248773313</v>
       </c>
-      <c r="G126" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G126" s="120">
+        <v>0.0170104912363424</v>
       </c>
       <c r="H126" s="122">
         <v>139.071286358343</v>
@@ -21192,7 +21166,7 @@
         <v>240.478962499819</v>
       </c>
       <c r="G127" s="121">
-        <v>59.9098532083731</v>
+        <v>59.9567724212992</v>
       </c>
       <c r="H127" s="123">
         <v>165.848762621644</v>
@@ -21368,10 +21342,8 @@
       <c r="F130" s="118">
         <v>19.0838134735714</v>
       </c>
-      <c r="G130" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G130" s="120">
+        <v>0.0379926400056145</v>
       </c>
       <c r="H130" s="122">
         <v>1.13562931167672</v>
@@ -21488,10 +21460,8 @@
       <c r="F132" s="118">
         <v>12.6091503168251</v>
       </c>
-      <c r="G132" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G132" s="120">
+        <v>0.0371240844771171</v>
       </c>
       <c r="H132" s="122">
         <v>0.679337356874512</v>
@@ -21962,10 +21932,8 @@
       <c r="F140" s="118">
         <v>60.452930531903</v>
       </c>
-      <c r="G140" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G140" s="120">
+        <v>0.0287374619258514</v>
       </c>
       <c r="H140" s="122">
         <v>143.167126819478</v>
@@ -22026,7 +21994,7 @@
         <v>305.48281638705</v>
       </c>
       <c r="G141" s="121">
-        <v>13.9208296386977</v>
+        <v>14.0246838251063</v>
       </c>
       <c r="H141" s="123">
         <v>166.195963811366</v>
@@ -25998,7 +25966,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>13.9208296386977</v>
+        <v>14.0246838251063</v>
       </c>
     </row>
     <row r="4">
